--- a/result.xlsx
+++ b/result.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="mini-sudoku" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="patches" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="queen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="tango" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="zip" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'mini-sudoku'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'patches'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'queen'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'tango'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'zip'!$A$1:$F$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +38,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,16 +64,62 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFD700"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F4B183"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -413,27 +481,1773 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>LinkedIn Games Tracker</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="1" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Total Records</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>30</v>
+          <t>Report Generated</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46227.67582268951</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Latest Game Data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Days</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Overall Statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AvgRank</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AvgTime</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Latest Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Performance Statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WinRate</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HintFreeRate</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MistakeFreeRate</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PerfectRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ActualDate</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>LocalRank</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>TimeElapsed</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>HintFree</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>MistakeFree</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <conditionalFormatting sqref="C2:C1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ActualDate</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>LocalRank</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>TimeElapsed</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>HintFree</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>MistakeFree</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>361</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <conditionalFormatting sqref="C2:C1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ActualDate</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>LocalRank</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>TimeElapsed</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>HintFree</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>MistakeFree</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <conditionalFormatting sqref="C2:C1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ActualDate</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>LocalRank</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>TimeElapsed</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>HintFree</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>MistakeFree</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <conditionalFormatting sqref="C2:C1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ActualDate</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>LocalRank</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>TimeElapsed</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>HintFree</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>MistakeFree</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <conditionalFormatting sqref="C2:C1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result.xlsx
+++ b/result.xlsx
@@ -15,11 +15,11 @@
     <sheet name="zip" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'mini-sudoku'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'patches'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'queen'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'tango'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'zip'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'mini-sudoku'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'patches'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'queen'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'tango'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'zip'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46227.67582268951</v>
+        <v>46228.97761925893</v>
       </c>
     </row>
     <row r="4">
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="E12" t="n">
-        <v>98.7</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="13">
@@ -610,16 +610,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="E13" t="n">
-        <v>53.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="14">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E14" t="n">
-        <v>88.59999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="16">
@@ -696,7 +696,7 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -712,16 +712,16 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -734,16 +734,16 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.05</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.45</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="26">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0.4</v>
@@ -848,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1107,8 +1107,80 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F13"/>
   <conditionalFormatting sqref="C2:C1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>1</formula>
@@ -1130,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1389,8 +1461,80 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F13"/>
   <conditionalFormatting sqref="C2:C1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>1</formula>
@@ -1412,7 +1556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1671,8 +1815,80 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F13"/>
   <conditionalFormatting sqref="C2:C1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>1</formula>
@@ -1694,7 +1910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1953,8 +2169,80 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F13"/>
   <conditionalFormatting sqref="C2:C1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>1</formula>
@@ -1976,7 +2264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2235,8 +2523,80 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F13"/>
   <conditionalFormatting sqref="C2:C1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>1</formula>

--- a/result.xlsx
+++ b/result.xlsx
@@ -82,13 +82,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -190,6 +189,215 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Average Rank Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!B19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Summary'!$A$20:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$B$20:$B$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!C19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Summary'!$A$20:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$C$20:$C$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!D19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Summary'!$A$20:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$D$20:$D$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Average Rank</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -481,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -504,7 +712,12 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46228.97761925893</v>
+        <v>46229.01925769333</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Latest Results</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -518,8 +731,59 @@
           <t>2026-07-24</t>
         </is>
       </c>
-    </row>
-    <row r="5"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PlayerName</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -529,6 +793,26 @@
       <c r="B6" t="n">
         <v>4</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -539,6 +823,26 @@
       <c r="B7" t="n">
         <v>3</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -583,6 +887,21 @@
           <t>AvgTime</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HintFreeRate</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MistakeFreeRate</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PerfectRate</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -602,6 +921,15 @@
       <c r="E12" t="n">
         <v>93.8</v>
       </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -621,6 +949,15 @@
       <c r="E13" t="n">
         <v>49.8</v>
       </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -640,205 +977,112 @@
       <c r="E14" t="n">
         <v>78.8</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Latest Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PlayerName</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>mini-sudoku</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>patches</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>queen</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>tango</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
+      <c r="F14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hien Thai</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3</v>
+          <t>Overall Trend</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>ActualDate</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Trang Nguyen</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C21" t="n">
         <v>2</v>
       </c>
-      <c r="F20" t="n">
-        <v>2</v>
+      <c r="D21" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Performance Statistics</t>
-        </is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PlayerName</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>WinRate</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>HintFreeRate</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>MistakeFreeRate</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>PerfectRate</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Hien Thai</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Nam Lê Hải</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Trang Nguyen</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0.4</v>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -860,322 +1104,322 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ActualDate</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>PlayerName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>LocalRank</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>TimeElapsed</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>HintFree</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>MistakeFree</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>308</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
+      <c r="E3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1214,322 +1458,322 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ActualDate</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>PlayerName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>LocalRank</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>TimeElapsed</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>HintFree</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>MistakeFree</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>361</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
+      <c r="E3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>238</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1568,322 +1812,322 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ActualDate</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>PlayerName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>LocalRank</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>TimeElapsed</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>HintFree</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>MistakeFree</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>203</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
+      <c r="E3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="C13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1922,322 +2166,322 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ActualDate</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>PlayerName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>LocalRank</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>TimeElapsed</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>HintFree</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>MistakeFree</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5" t="n">
+      <c r="C2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
+      <c r="E3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2276,322 +2520,322 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ActualDate</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>PlayerName</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>LocalRank</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>TimeElapsed</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>HintFree</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>MistakeFree</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="n">
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
+      <c r="E3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>224</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5" t="n">
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="E9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Hien Thai</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Nam Lê Hải</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="C12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Trang Nguyen</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result.xlsx
+++ b/result.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Raw" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$H$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$H$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Summary'!$A$20:$A$24</f>
+              <f>'Summary'!$A$20:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$B$20:$B$24</f>
+              <f>'Summary'!$B$20:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -259,12 +259,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Summary'!$A$20:$A$24</f>
+              <f>'Summary'!$A$20:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$C$20:$C$24</f>
+              <f>'Summary'!$C$20:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -291,12 +291,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Summary'!$A$20:$A$24</f>
+              <f>'Summary'!$A$20:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$D$20:$D$24</f>
+              <f>'Summary'!$D$20:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46230.59780078298</v>
+        <v>46237.42955782326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -764,16 +764,16 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -794,16 +794,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -824,16 +824,16 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -902,25 +902,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="E12" t="n">
-        <v>85.7</v>
+        <v>75.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4</v>
+        <v>0.4153846153846154</v>
       </c>
     </row>
     <row r="13">
@@ -930,25 +930,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="E13" t="n">
-        <v>45.5</v>
+        <v>42.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.9846153846153847</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0.4461538461538462</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5</v>
+        <v>0.4461538461538462</v>
       </c>
     </row>
     <row r="14">
@@ -958,25 +958,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="E14" t="n">
-        <v>78.2</v>
+        <v>63.1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5230769230769231</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4</v>
+        <v>0.4769230769230769</v>
       </c>
     </row>
     <row r="18">
@@ -1102,6 +1102,118 @@
       </c>
       <c r="D25" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -4231,8 +4343,3578 @@
         <v>0</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.535992</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.535992</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.535992</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:15.776948</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:15.776948</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:15.776948</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:17.281549</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:17.281549</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:17.281549</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.918974</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.918974</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.918974</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.146795</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.146795</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:42:16.146795</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.926615</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.926615</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.926615</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.034786</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.034786</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.034786</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:05.755876</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:05.755876</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:05.755876</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:05.347956</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:05.347956</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:05.347956</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.505904</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.505904</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:04.505904</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:07.330246</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:07.330246</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:07.330246</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:06.230708</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:06.230708</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:06.230708</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:08.345877</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:08.345877</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:08.345877</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:07.868534</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:07.868534</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:07.868534</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:06.750549</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:06.750549</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:06.750549</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:05.650656</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:05.650656</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:05.650656</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:04.587002</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:04.587002</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:04.587002</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:06.556715</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:06.556715</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:06.556715</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:06.070789</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:06.070789</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G147" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:06.070789</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:05.189499</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:05.189499</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G150" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:05.189499</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:05.611490</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="G152" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:05.611490</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:05.611490</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:04.756595</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G155" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:04.756595</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:04.756595</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G157" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:06.507419</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:06.507419</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="G159" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:06.507419</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:06.042244</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="G161" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:06.042244</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="G162" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:06.042244</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:05.202915</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:05.202915</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="G165" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:05.202915</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="G166" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.434292</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="G167" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.434292</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.434292</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="G169" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:04.622805</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G170" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:04.622805</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G171" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:04.622805</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G172" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:06.233542</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:06.233542</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="G174" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:06.233542</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G175" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.820427</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G176" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.820427</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G177" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.820427</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G178" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.046109</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.046109</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G180" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:00:05.046109</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G181" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:05.674802</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="G182" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:05.674802</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:05.674802</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>mini-sudoku</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>197</v>
+      </c>
+      <c r="G184" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:04.678300</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:04.678300</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G186" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:04.678300</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>patches</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="G187" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:06.473139</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="G188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:06.473139</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="G189" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:06.473139</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>queen</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="G190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:06.059056</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:06.059056</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G192" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:06.059056</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>tango</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G193" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:05.260583</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>Trang Nguyen</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="G194" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:05.260583</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>Nam Lê Hải</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="G195" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T07:00:05.260583</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>Hien Thai</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="G196" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H91"/>
+  <autoFilter ref="A1:H196"/>
   <conditionalFormatting sqref="C2:C1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>1</formula>

--- a/result.xlsx
+++ b/result.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46237.42955782326</v>
+        <v>46237.70170223402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -794,16 +794,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -833,7 +833,7 @@
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -905,22 +905,22 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="E12" t="n">
-        <v>75.5</v>
+        <v>72.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9846153846153847</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4153846153846154</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4153846153846154</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -936,10 +936,10 @@
         <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="E13" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="F13" t="n">
         <v>0.9846153846153847</v>
@@ -961,19 +961,19 @@
         <v>65</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="E14" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9384615384615385</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5230769230769231</v>
+        <v>0.5076923076923077</v>
       </c>
       <c r="H14" t="n">
         <v>0.4769230769230769</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -7406,7 +7406,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:05.674802</t>
+          <t>2026-08-03T16:50:26.160458</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -7428,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G182" s="4" t="n">
         <v>1</v>
@@ -7440,7 +7440,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:05.674802</t>
+          <t>2026-08-03T16:50:26.160458</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -7462,7 +7462,7 @@
         <v>2</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="G183" s="4" t="n">
         <v>1</v>
@@ -7474,7 +7474,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:05.674802</t>
+          <t>2026-08-03T16:50:26.160458</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -7496,7 +7496,7 @@
         <v>3</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="G184" s="4" t="n">
         <v>1</v>
@@ -7508,7 +7508,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:04.678300</t>
+          <t>2026-08-03T16:50:25.344160</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -7523,14 +7523,14 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Hien Thai</t>
+          <t>Nam Lê Hải</t>
         </is>
       </c>
       <c r="E185" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G185" s="4" t="n">
         <v>1</v>
@@ -7542,7 +7542,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:04.678300</t>
+          <t>2026-08-03T16:50:25.344160</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -7557,14 +7557,14 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Nam Lê Hải</t>
+          <t>Hien Thai</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="G186" s="4" t="n">
         <v>1</v>
@@ -7576,7 +7576,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:04.678300</t>
+          <t>2026-08-03T16:50:25.344160</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -7598,7 +7598,7 @@
         <v>3</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="G187" s="4" t="n">
         <v>1</v>
@@ -7610,7 +7610,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:06.473139</t>
+          <t>2026-08-03T16:50:27.032153</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -7625,26 +7625,26 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Nam Lê Hải</t>
+          <t>Hien Thai</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G188" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H188" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:06.473139</t>
+          <t>2026-08-03T16:50:27.032153</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -7666,10 +7666,10 @@
         <v>2</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G189" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" s="4" t="n">
         <v>1</v>
@@ -7678,7 +7678,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:06.473139</t>
+          <t>2026-08-03T16:50:27.032153</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -7693,26 +7693,26 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Hien Thai</t>
+          <t>Nam Lê Hải</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="G190" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H190" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:06.059056</t>
+          <t>2026-08-03T16:50:26.605873</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -7734,7 +7734,7 @@
         <v>1</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G191" s="4" t="n">
         <v>1</v>
@@ -7746,7 +7746,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:06.059056</t>
+          <t>2026-08-03T16:50:26.605873</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -7768,19 +7768,19 @@
         <v>2</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G192" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H192" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:06.059056</t>
+          <t>2026-08-03T16:50:26.605873</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -7802,19 +7802,19 @@
         <v>3</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="G193" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H193" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:05.260583</t>
+          <t>2026-08-03T16:50:25.760658</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -7829,14 +7829,14 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Trang Nguyen</t>
+          <t>Hien Thai</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G194" s="4" t="n">
         <v>1</v>
@@ -7848,7 +7848,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:05.260583</t>
+          <t>2026-08-03T16:50:25.760658</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -7863,14 +7863,14 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Nam Lê Hải</t>
+          <t>Trang Nguyen</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="G195" s="4" t="n">
         <v>1</v>
@@ -7882,7 +7882,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T07:00:05.260583</t>
+          <t>2026-08-03T16:50:25.760658</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -7897,17 +7897,17 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Hien Thai</t>
+          <t>Nam Lê Hải</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>320</v>
+        <v>74</v>
       </c>
       <c r="G196" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H196" s="4" t="n">
         <v>0</v>

--- a/result.xlsx
+++ b/result.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46237.70170223402</v>
+        <v>46237.70492016515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:26.160458</t>
+          <t>2026-08-03T16:55:04.189212</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -7440,7 +7440,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:26.160458</t>
+          <t>2026-08-03T16:55:04.189212</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -7474,7 +7474,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:26.160458</t>
+          <t>2026-08-03T16:55:04.189212</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:25.344160</t>
+          <t>2026-08-03T16:55:03.274225</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -7542,7 +7542,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:25.344160</t>
+          <t>2026-08-03T16:55:03.274225</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -7576,7 +7576,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:25.344160</t>
+          <t>2026-08-03T16:55:03.274225</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -7610,7 +7610,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:27.032153</t>
+          <t>2026-08-03T16:55:05.059370</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -7644,7 +7644,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:27.032153</t>
+          <t>2026-08-03T16:55:05.059370</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -7678,7 +7678,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:27.032153</t>
+          <t>2026-08-03T16:55:05.059370</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:26.605873</t>
+          <t>2026-08-03T16:55:04.593570</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -7746,7 +7746,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:26.605873</t>
+          <t>2026-08-03T16:55:04.593570</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -7780,7 +7780,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:26.605873</t>
+          <t>2026-08-03T16:55:04.593570</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -7814,7 +7814,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:25.760658</t>
+          <t>2026-08-03T16:55:03.731316</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -7848,7 +7848,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:25.760658</t>
+          <t>2026-08-03T16:55:03.731316</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -7882,7 +7882,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T16:50:25.760658</t>
+          <t>2026-08-03T16:55:03.731316</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
